--- a/docs/01_db/model.xlsx
+++ b/docs/01_db/model.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29F99556-6372-4656-B706-5D41D3B4F70B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A89AC2-5309-417F-B0A4-B5A52D65B202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{626A7CE0-792B-48AD-BD3B-147FEC4A9A40}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{626A7CE0-792B-48AD-BD3B-147FEC4A9A40}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="53">
   <si>
     <t>社員ID</t>
     <rPh sb="0" eb="2">
@@ -178,6 +179,153 @@
     <rPh sb="3" eb="6">
       <t>シンジュクク</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>論理名</t>
+    <rPh sb="0" eb="3">
+      <t>ロンリメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>物理名</t>
+    <rPh sb="0" eb="3">
+      <t>ブツリメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データ型</t>
+    <rPh sb="3" eb="4">
+      <t>ガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>桁</t>
+    <rPh sb="0" eb="1">
+      <t>ケタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>備考</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>integer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>varchar</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>date</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>emp_id</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>emp_name</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dept_id</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>birthday</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>phone_number</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PK</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FK</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>email</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>address</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>delete_flag</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0:男性,1:女性,2:その他</t>
+    <rPh sb="2" eb="4">
+      <t>ダンセイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジョセイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NOT NULL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>gender</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TRUE:削除済み</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dept_name</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>user_id</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Employee</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Department</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>User</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -185,7 +333,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -218,7 +366,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -234,6 +382,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -270,7 +430,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -290,6 +450,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -628,7 +794,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3478165-C954-42EB-9C0B-F0C6E0F4D13C}">
   <dimension ref="C2:Q4"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.1640625" customWidth="1"/>
@@ -641,7 +807,7 @@
     <col min="17" max="17" width="10.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="3:17">
       <c r="C2" t="s">
         <v>7</v>
       </c>
@@ -652,7 +818,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="3:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="3:17">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -693,7 +859,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="3:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="3:17">
       <c r="C4" s="3">
         <v>1</v>
       </c>
@@ -718,7 +884,7 @@
       <c r="J4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="1">
+      <c r="K4" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M4" s="3">
@@ -741,4 +907,395 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9394CB66-45E4-41BC-B269-3DD978F3C082}">
+  <dimension ref="B1:I21"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="2" max="2" width="13.5" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="8" max="8" width="11.58203125" customWidth="1"/>
+    <col min="9" max="9" width="19" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:9">
+      <c r="B1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="2:9">
+      <c r="B2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9">
+      <c r="B3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="2:9">
+      <c r="B4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="1">
+        <v>10</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="2:9">
+      <c r="B5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="2:9">
+      <c r="B6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="2:9">
+      <c r="B7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9">
+      <c r="B8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="1">
+        <v>11</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="2:9">
+      <c r="B9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="1">
+        <v>100</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="2:9">
+      <c r="B10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="1">
+        <v>100</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="2:9">
+      <c r="B11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9">
+      <c r="B13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9">
+      <c r="B14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9">
+      <c r="B15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="1">
+        <v>2</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="2:9">
+      <c r="B16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="1">
+        <v>10</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="1">
+        <v>10</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="2:9">
+      <c r="B21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="1">
+        <v>10</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I21" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="D9" r:id="rId1" display="tt@mail.com" xr:uid="{F2C6AE3D-9B22-4027-981C-8AF5D448A51F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/01_db/model.xlsx
+++ b/docs/01_db/model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A89AC2-5309-417F-B0A4-B5A52D65B202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB76579-576B-4A04-B292-515402C19EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{626A7CE0-792B-48AD-BD3B-147FEC4A9A40}"/>
   </bookViews>
@@ -333,7 +333,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -794,7 +794,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3478165-C954-42EB-9C0B-F0C6E0F4D13C}">
   <dimension ref="C2:Q4"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.1640625" customWidth="1"/>
@@ -807,7 +807,7 @@
     <col min="17" max="17" width="10.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:17">
+    <row r="2" spans="3:17" x14ac:dyDescent="0.55000000000000004">
       <c r="C2" t="s">
         <v>7</v>
       </c>
@@ -818,7 +818,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="3:17">
+    <row r="3" spans="3:17" x14ac:dyDescent="0.55000000000000004">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -859,7 +859,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="3:17">
+    <row r="4" spans="3:17" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="3">
         <v>1</v>
       </c>
@@ -912,7 +912,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9394CB66-45E4-41BC-B269-3DD978F3C082}">
   <dimension ref="B1:I21"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="13.5" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
@@ -921,7 +921,7 @@
     <col min="9" max="9" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9">
+    <row r="1" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" t="s">
         <v>50</v>
       </c>
@@ -929,7 +929,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="2:9">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="7" t="s">
         <v>24</v>
       </c>
@@ -955,7 +955,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="2:9">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="1" t="s">
         <v>32</v>
       </c>
@@ -966,7 +966,7 @@
         <v>29</v>
       </c>
       <c r="E3" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>28</v>
@@ -977,7 +977,7 @@
       </c>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="2:9">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="1" t="s">
         <v>33</v>
       </c>
@@ -997,7 +997,7 @@
       </c>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="1" t="s">
         <v>34</v>
       </c>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="2:9">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="1" t="s">
         <v>35</v>
       </c>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="2:9">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="1" t="s">
         <v>45</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="2:9">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="1" t="s">
         <v>36</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>30</v>
       </c>
       <c r="E8" s="1">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="2:9">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="1" t="s">
         <v>40</v>
       </c>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="2:9">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="1" t="s">
         <v>41</v>
       </c>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="2:9">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="1" t="s">
         <v>42</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="2:9">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" t="s">
         <v>51</v>
       </c>
@@ -1147,7 +1147,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:9">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="7" t="s">
         <v>24</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="2:9">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="1" t="s">
         <v>34</v>
       </c>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="2:9">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="1" t="s">
         <v>48</v>
       </c>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="I16" s="1"/>
     </row>
-    <row r="18" spans="2:9">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" t="s">
         <v>52</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="2:9">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="7" t="s">
         <v>24</v>
       </c>
@@ -1249,7 +1249,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="2:9">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="1" t="s">
         <v>49</v>
       </c>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="I20" s="1"/>
     </row>
-    <row r="21" spans="2:9">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="1" t="s">
         <v>11</v>
       </c>
